--- a/PolData.xlsx
+++ b/PolData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/erikgahnerlarsen/PolData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71D36641-5A20-3345-AE57-193CB941F764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBC7F553-CC77-BA47-BBD8-36F863E979A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="17380" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5509" uniqueCount="2932">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5510" uniqueCount="2933">
   <si>
     <t>name</t>
   </si>
@@ -8824,6 +8824,9 @@
   </si>
   <si>
     <t>minorities, risk</t>
+  </si>
+  <si>
+    <t>https://popu-list.github.io/Data/The%20PopuList%204.0.csv</t>
   </si>
 </sst>
 </file>
@@ -38776,7 +38779,7 @@
         <v>1989</v>
       </c>
       <c r="L561">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="M561" t="s">
         <v>215</v>
@@ -38785,6 +38788,9 @@
         <v>362</v>
       </c>
       <c r="P561" s="2"/>
+      <c r="Q561" s="2" t="s">
+        <v>2932</v>
+      </c>
       <c r="T561" s="2"/>
       <c r="W561" t="s">
         <v>471</v>
@@ -38796,7 +38802,7 @@
         <v>2527</v>
       </c>
       <c r="AB561">
-        <v>20230921</v>
+        <v>20260627</v>
       </c>
     </row>
     <row r="562" spans="1:28" x14ac:dyDescent="0.2">
@@ -42901,8 +42907,9 @@
     <hyperlink ref="C23" r:id="rId1033" xr:uid="{18287E65-0749-0C44-847F-A336813B4C34}"/>
     <hyperlink ref="Q371" r:id="rId1034" xr:uid="{E1195149-30EC-CE42-B1F5-3C5844CB789A}"/>
     <hyperlink ref="P371" r:id="rId1035" xr:uid="{010688ED-D3BC-9547-AF18-BBBFB85B857F}"/>
+    <hyperlink ref="Q561" r:id="rId1036" xr:uid="{FD644AB9-CE91-9440-8E20-95A5CD3B71A5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1036"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1037"/>
 </worksheet>
 </file>